--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/120.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/120.xlsx
@@ -426,13 +426,13 @@
         <v>-5.926778212054566</v>
       </c>
       <c r="E2">
-        <v>-12.08536708467787</v>
+        <v>-12.68908965395846</v>
       </c>
       <c r="F2">
-        <v>-6.408077040199855</v>
+        <v>-7.513451110954901</v>
       </c>
       <c r="G2">
-        <v>-9.94605850485096</v>
+        <v>-10.90446805956105</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.57772053319061</v>
       </c>
       <c r="E3">
-        <v>-12.86547824503123</v>
+        <v>-13.54355835751776</v>
       </c>
       <c r="F3">
-        <v>-6.818098897633607</v>
+        <v>-6.6236206030706</v>
       </c>
       <c r="G3">
-        <v>-10.47583186531837</v>
+        <v>-10.59752751934198</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.282195533878739</v>
       </c>
       <c r="E4">
-        <v>-13.56706113761757</v>
+        <v>-14.09035800852194</v>
       </c>
       <c r="F4">
-        <v>-6.554354453373504</v>
+        <v>-7.212658638288445</v>
       </c>
       <c r="G4">
-        <v>-10.58769850963588</v>
+        <v>-10.77475757478686</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.073772010774649</v>
       </c>
       <c r="E5">
-        <v>-13.92155008293801</v>
+        <v>-14.92505086608974</v>
       </c>
       <c r="F5">
-        <v>-6.482287123838475</v>
+        <v>-7.187587385867602</v>
       </c>
       <c r="G5">
-        <v>-10.02581285743754</v>
+        <v>-10.76899722554853</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.941921113104378</v>
       </c>
       <c r="E6">
-        <v>-14.45599152837525</v>
+        <v>-15.29758125185674</v>
       </c>
       <c r="F6">
-        <v>-6.49144609107394</v>
+        <v>-7.16307478570843</v>
       </c>
       <c r="G6">
-        <v>-11.11725999518878</v>
+        <v>-10.87632180138616</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.871300623807844</v>
       </c>
       <c r="E7">
-        <v>-15.31454491548947</v>
+        <v>-17.34084230953962</v>
       </c>
       <c r="F7">
-        <v>-6.134463732527692</v>
+        <v>-6.83813832043462</v>
       </c>
       <c r="G7">
-        <v>-10.49804893643242</v>
+        <v>-10.54151308881751</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.850589234318301</v>
       </c>
       <c r="E8">
-        <v>-17.17329329972983</v>
+        <v>-16.83283809535916</v>
       </c>
       <c r="F8">
-        <v>-6.246183494847015</v>
+        <v>-7.041713025849432</v>
       </c>
       <c r="G8">
-        <v>-10.93067433804992</v>
+        <v>-11.49242756842669</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.855259531580139</v>
       </c>
       <c r="E9">
-        <v>-17.84132472839335</v>
+        <v>-18.04927225482557</v>
       </c>
       <c r="F9">
-        <v>-6.001614957737533</v>
+        <v>-7.291149874942976</v>
       </c>
       <c r="G9">
-        <v>-10.38853608999333</v>
+        <v>-10.89580767243031</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.873538916319125</v>
       </c>
       <c r="E10">
-        <v>-18.31517972008196</v>
+        <v>-18.88984307165533</v>
       </c>
       <c r="F10">
-        <v>-6.356078827951753</v>
+        <v>-6.796311063501949</v>
       </c>
       <c r="G10">
-        <v>-10.45117161159634</v>
+        <v>-10.37958768540068</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.881971119860519</v>
       </c>
       <c r="E11">
-        <v>-19.48623856999151</v>
+        <v>-18.57629605983825</v>
       </c>
       <c r="F11">
-        <v>-6.076613726922041</v>
+        <v>-7.334674864616998</v>
       </c>
       <c r="G11">
-        <v>-10.1029684317758</v>
+        <v>-10.2817180276232</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.875876918477657</v>
       </c>
       <c r="E12">
-        <v>-19.52377509104109</v>
+        <v>-19.17062657402693</v>
       </c>
       <c r="F12">
-        <v>-5.824904259839841</v>
+        <v>-6.870290717929872</v>
       </c>
       <c r="G12">
-        <v>-9.543754389827647</v>
+        <v>-10.37781654353717</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.840776650695362</v>
       </c>
       <c r="E13">
-        <v>-19.88836706187264</v>
+        <v>-20.43172054415697</v>
       </c>
       <c r="F13">
-        <v>-5.650520025931931</v>
+        <v>-6.863910362723045</v>
       </c>
       <c r="G13">
-        <v>-9.71144345302835</v>
+        <v>-9.640654057762115</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.784663172014852</v>
       </c>
       <c r="E14">
-        <v>-22.15350070356133</v>
+        <v>-20.71758046589116</v>
       </c>
       <c r="F14">
-        <v>-5.902953246617486</v>
+        <v>-6.961129713680605</v>
       </c>
       <c r="G14">
-        <v>-8.325708680109139</v>
+        <v>-9.279778109617242</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.707993527370155</v>
       </c>
       <c r="E15">
-        <v>-21.31883501683757</v>
+        <v>-21.47442432679311</v>
       </c>
       <c r="F15">
-        <v>-5.593477314416675</v>
+        <v>-6.882089326999895</v>
       </c>
       <c r="G15">
-        <v>-8.732273467241495</v>
+        <v>-8.124328194955272</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.632680814623902</v>
       </c>
       <c r="E16">
-        <v>-22.54953386942814</v>
+        <v>-23.46623739127486</v>
       </c>
       <c r="F16">
-        <v>-5.129147409657152</v>
+        <v>-6.333574762819837</v>
       </c>
       <c r="G16">
-        <v>-7.542456779336351</v>
+        <v>-7.885032031740133</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.568755167172464</v>
       </c>
       <c r="E17">
-        <v>-23.11328359864302</v>
+        <v>-23.65840771426436</v>
       </c>
       <c r="F17">
-        <v>-5.396344728739392</v>
+        <v>-6.141028985400146</v>
       </c>
       <c r="G17">
-        <v>-7.437654839199642</v>
+        <v>-7.358334168078705</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.537414750126614</v>
       </c>
       <c r="E18">
-        <v>-23.89564541057819</v>
+        <v>-24.69923670866132</v>
       </c>
       <c r="F18">
-        <v>-5.024842954360395</v>
+        <v>-6.099546976357041</v>
       </c>
       <c r="G18">
-        <v>-7.115343436041739</v>
+        <v>-5.75512303759369</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.54017986094657</v>
       </c>
       <c r="E19">
-        <v>-25.12235014909399</v>
+        <v>-24.3278746691883</v>
       </c>
       <c r="F19">
-        <v>-4.894313120956918</v>
+        <v>-5.605796170879921</v>
       </c>
       <c r="G19">
-        <v>-5.895711975009919</v>
+        <v>-6.760138452405637</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.58259087499755</v>
       </c>
       <c r="E20">
-        <v>-25.51848294138896</v>
+        <v>-25.00375847178112</v>
       </c>
       <c r="F20">
-        <v>-4.462321699137711</v>
+        <v>-5.650894572380932</v>
       </c>
       <c r="G20">
-        <v>-6.284237599498786</v>
+        <v>-6.637426460901472</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.649781067984964</v>
       </c>
       <c r="E21">
-        <v>-26.52967760187973</v>
+        <v>-25.25031123912873</v>
       </c>
       <c r="F21">
-        <v>-4.641376281790253</v>
+        <v>-5.30277225657861</v>
       </c>
       <c r="G21">
-        <v>-6.365455213213727</v>
+        <v>-6.667168402026284</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.733489582768337</v>
       </c>
       <c r="E22">
-        <v>-27.56089717443242</v>
+        <v>-26.44010438600801</v>
       </c>
       <c r="F22">
-        <v>-4.005333855002166</v>
+        <v>-4.454548870504734</v>
       </c>
       <c r="G22">
-        <v>-5.881264754276541</v>
+        <v>-7.28758780990448</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.812587506560914</v>
       </c>
       <c r="E23">
-        <v>-27.86411473703801</v>
+        <v>-27.66636986254507</v>
       </c>
       <c r="F23">
-        <v>-3.736391292001112</v>
+        <v>-4.874225395125484</v>
       </c>
       <c r="G23">
-        <v>-6.318071374910137</v>
+        <v>-6.960476115714633</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.877598402814463</v>
       </c>
       <c r="E24">
-        <v>-27.46833516571564</v>
+        <v>-28.6312608763074</v>
       </c>
       <c r="F24">
-        <v>-3.514132420122425</v>
+        <v>-4.94507881407633</v>
       </c>
       <c r="G24">
-        <v>-6.273326041401348</v>
+        <v>-6.817218878593751</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.911208081477357</v>
       </c>
       <c r="E25">
-        <v>-27.97598163044949</v>
+        <v>-27.67917638703876</v>
       </c>
       <c r="F25">
-        <v>-3.52789957564534</v>
+        <v>-4.140427137000982</v>
       </c>
       <c r="G25">
-        <v>-5.76698141171536</v>
+        <v>-6.267631903073802</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.9092022476972</v>
       </c>
       <c r="E26">
-        <v>-28.3032997317239</v>
+        <v>-27.47213908388208</v>
       </c>
       <c r="F26">
-        <v>-3.180532687564682</v>
+        <v>-3.682298232753363</v>
       </c>
       <c r="G26">
-        <v>-7.068906413762382</v>
+        <v>-7.291298931454003</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.862878981309401</v>
       </c>
       <c r="E27">
-        <v>-28.19268269713854</v>
+        <v>-27.18939475226517</v>
       </c>
       <c r="F27">
-        <v>-3.064962540238446</v>
+        <v>-4.060122161146793</v>
       </c>
       <c r="G27">
-        <v>-6.174234792319883</v>
+        <v>-7.246268891028836</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.778070995881875</v>
       </c>
       <c r="E28">
-        <v>-28.31405485749212</v>
+        <v>-28.61557877081884</v>
       </c>
       <c r="F28">
-        <v>-3.358998923469638</v>
+        <v>-3.943546360564254</v>
       </c>
       <c r="G28">
-        <v>-6.496688548935976</v>
+        <v>-7.167772545747177</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.65788519079154</v>
       </c>
       <c r="E29">
-        <v>-28.4667776434008</v>
+        <v>-28.6052176222893</v>
       </c>
       <c r="F29">
-        <v>-3.120410459896855</v>
+        <v>-3.836793495922227</v>
       </c>
       <c r="G29">
-        <v>-7.068631638482623</v>
+        <v>-6.933511722297269</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.517247480172545</v>
       </c>
       <c r="E30">
-        <v>-28.37247217219107</v>
+        <v>-26.90844369635529</v>
       </c>
       <c r="F30">
-        <v>-3.335745369513241</v>
+        <v>-4.080249479626113</v>
       </c>
       <c r="G30">
-        <v>-6.745542257122991</v>
+        <v>-8.237429672758934</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.364947147276601</v>
       </c>
       <c r="E31">
-        <v>-27.95871455905824</v>
+        <v>-28.0980828751183</v>
       </c>
       <c r="F31">
-        <v>-3.176364373595246</v>
+        <v>-4.265016489515645</v>
       </c>
       <c r="G31">
-        <v>-7.250367346406454</v>
+        <v>-7.897820669158338</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.215990970318176</v>
       </c>
       <c r="E32">
-        <v>-27.02884223479722</v>
+        <v>-27.54579924209084</v>
       </c>
       <c r="F32">
-        <v>-3.304711860247247</v>
+        <v>-3.875745534765418</v>
       </c>
       <c r="G32">
-        <v>-6.552295782359113</v>
+        <v>-7.630984077602001</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.075943594893106</v>
       </c>
       <c r="E33">
-        <v>-26.97096380850519</v>
+        <v>-27.71080324950833</v>
       </c>
       <c r="F33">
-        <v>-2.996884565904409</v>
+        <v>-3.976257806247656</v>
       </c>
       <c r="G33">
-        <v>-6.513641852642583</v>
+        <v>-6.767590490414537</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.953354141541463</v>
       </c>
       <c r="E34">
-        <v>-26.05309194036449</v>
+        <v>-27.0665553663331</v>
       </c>
       <c r="F34">
-        <v>-3.320885456908672</v>
+        <v>-3.729467329738811</v>
       </c>
       <c r="G34">
-        <v>-6.606022625915945</v>
+        <v>-7.159433281533753</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.847176503699489</v>
       </c>
       <c r="E35">
-        <v>-27.135573838684</v>
+        <v>-25.56884410082827</v>
       </c>
       <c r="F35">
-        <v>-3.170464277207276</v>
+        <v>-3.997595867899329</v>
       </c>
       <c r="G35">
-        <v>-5.49942974232254</v>
+        <v>-6.658918522542421</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.759938824703981</v>
       </c>
       <c r="E36">
-        <v>-25.59164496745689</v>
+        <v>-26.44337847271556</v>
       </c>
       <c r="F36">
-        <v>-3.027777917196886</v>
+        <v>-4.076338517867936</v>
       </c>
       <c r="G36">
-        <v>-6.243080897354567</v>
+        <v>-7.276881505630477</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.687534175569232</v>
       </c>
       <c r="E37">
-        <v>-25.22786359347271</v>
+        <v>-25.97557352230119</v>
       </c>
       <c r="F37">
-        <v>-3.449970950517269</v>
+        <v>-3.971691982093444</v>
       </c>
       <c r="G37">
-        <v>-5.603963528270568</v>
+        <v>-7.166474811895783</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.631225787776199</v>
       </c>
       <c r="E38">
-        <v>-24.93541021358335</v>
+        <v>-25.19736884950506</v>
       </c>
       <c r="F38">
-        <v>-3.683972209905982</v>
+        <v>-4.09723551742216</v>
       </c>
       <c r="G38">
-        <v>-6.616735551281027</v>
+        <v>-7.166739655538924</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.588027349376765</v>
       </c>
       <c r="E39">
-        <v>-23.78376040327068</v>
+        <v>-24.63541239599721</v>
       </c>
       <c r="F39">
-        <v>-3.285861800588729</v>
+        <v>-4.443808176986224</v>
       </c>
       <c r="G39">
-        <v>-5.761191267567174</v>
+        <v>-7.017255282258673</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.560167463857963</v>
       </c>
       <c r="E40">
-        <v>-23.92346835488132</v>
+        <v>-24.08118151914645</v>
       </c>
       <c r="F40">
-        <v>-3.22426435086067</v>
+        <v>-4.208943797873596</v>
       </c>
       <c r="G40">
-        <v>-5.082453289469178</v>
+        <v>-6.119991503658925</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.545147813254275</v>
       </c>
       <c r="E41">
-        <v>-22.9592384983241</v>
+        <v>-23.1549500879876</v>
       </c>
       <c r="F41">
-        <v>-3.854694123884439</v>
+        <v>-3.670498831830381</v>
       </c>
       <c r="G41">
-        <v>-5.891527445448281</v>
+        <v>-6.190072442179757</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.543526530295813</v>
       </c>
       <c r="E42">
-        <v>-23.16397533668489</v>
+        <v>-24.5897699064739</v>
       </c>
       <c r="F42">
-        <v>-3.589294311016223</v>
+        <v>-3.883003658975877</v>
       </c>
       <c r="G42">
-        <v>-5.203748367482535</v>
+        <v>-6.728535984687754</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.551626326800735</v>
       </c>
       <c r="E43">
-        <v>-22.20121270570615</v>
+        <v>-22.75216949584937</v>
       </c>
       <c r="F43">
-        <v>-3.675698138350769</v>
+        <v>-4.013965844094269</v>
       </c>
       <c r="G43">
-        <v>-4.733343020170873</v>
+        <v>-6.082893530345852</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.568541708705162</v>
       </c>
       <c r="E44">
-        <v>-21.8620073601616</v>
+        <v>-22.60753456451838</v>
       </c>
       <c r="F44">
-        <v>-3.681850043979293</v>
+        <v>-4.253809394605038</v>
       </c>
       <c r="G44">
-        <v>-4.846106822329529</v>
+        <v>-6.212892032581953</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.590009796032593</v>
       </c>
       <c r="E45">
-        <v>-22.13794086687098</v>
+        <v>-22.12934582320442</v>
       </c>
       <c r="F45">
-        <v>-3.487535662978535</v>
+        <v>-3.996974263327519</v>
       </c>
       <c r="G45">
-        <v>-4.724242330483418</v>
+        <v>-6.669515578813628</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.613709464905916</v>
       </c>
       <c r="E46">
-        <v>-21.20664660177155</v>
+        <v>-21.64644746892249</v>
       </c>
       <c r="F46">
-        <v>-3.364963159947183</v>
+        <v>-4.614946605620442</v>
       </c>
       <c r="G46">
-        <v>-4.621714735132189</v>
+        <v>-6.046782099603481</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.635073009698497</v>
       </c>
       <c r="E47">
-        <v>-20.98478307471375</v>
+        <v>-20.08977547183779</v>
       </c>
       <c r="F47">
-        <v>-3.757681842475322</v>
+        <v>-4.530870034128634</v>
       </c>
       <c r="G47">
-        <v>-4.689633887415877</v>
+        <v>-6.566064341256943</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.651569866971267</v>
       </c>
       <c r="E48">
-        <v>-19.42453358316299</v>
+        <v>-19.90188455678554</v>
       </c>
       <c r="F48">
-        <v>-3.630392271374835</v>
+        <v>-4.381696022835647</v>
       </c>
       <c r="G48">
-        <v>-4.507345318386987</v>
+        <v>-6.414461218831558</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.659690237200558</v>
       </c>
       <c r="E49">
-        <v>-18.92022460377279</v>
+        <v>-19.6806459591408</v>
       </c>
       <c r="F49">
-        <v>-3.79018661453676</v>
+        <v>-4.143496359065104</v>
       </c>
       <c r="G49">
-        <v>-5.224296923644791</v>
+        <v>-6.205562484758007</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.657547982959053</v>
       </c>
       <c r="E50">
-        <v>-19.38603702562379</v>
+        <v>-18.96496592696857</v>
       </c>
       <c r="F50">
-        <v>-3.694126140382822</v>
+        <v>-4.326529210977229</v>
       </c>
       <c r="G50">
-        <v>-4.527476745811295</v>
+        <v>-5.831441043910509</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.643724832772187</v>
       </c>
       <c r="E51">
-        <v>-18.04661856905707</v>
+        <v>-18.64897806766135</v>
       </c>
       <c r="F51">
-        <v>-4.059315262982877</v>
+        <v>-4.460868648960296</v>
       </c>
       <c r="G51">
-        <v>-4.806390207494893</v>
+        <v>-5.768080512834397</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.619382489478938</v>
       </c>
       <c r="E52">
-        <v>-16.61497773932415</v>
+        <v>-17.55615766318233</v>
       </c>
       <c r="F52">
-        <v>-3.831490456664378</v>
+        <v>-4.450218226678965</v>
       </c>
       <c r="G52">
-        <v>-4.898026108021919</v>
+        <v>-4.584984232373975</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.587222412417912</v>
       </c>
       <c r="E53">
-        <v>-17.32536851385542</v>
+        <v>-17.61775849510867</v>
       </c>
       <c r="F53">
-        <v>-3.968701945325094</v>
+        <v>-4.624612754675327</v>
       </c>
       <c r="G53">
-        <v>-5.012935143690022</v>
+        <v>-5.858974851160627</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.551043929523673</v>
       </c>
       <c r="E54">
-        <v>-17.12375632255992</v>
+        <v>-16.36401876676707</v>
       </c>
       <c r="F54">
-        <v>-4.074240107529978</v>
+        <v>-4.402342005002273</v>
       </c>
       <c r="G54">
-        <v>-5.218202209306993</v>
+        <v>-6.157884007901423</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.514987292575124</v>
       </c>
       <c r="E55">
-        <v>-14.95034239342258</v>
+        <v>-15.71724399509556</v>
       </c>
       <c r="F55">
-        <v>-4.155188067985836</v>
+        <v>-4.747084692381048</v>
       </c>
       <c r="G55">
-        <v>-4.780369319556221</v>
+        <v>-6.101180983904785</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.482573721079132</v>
       </c>
       <c r="E56">
-        <v>-15.24174516734216</v>
+        <v>-16.68315844398364</v>
       </c>
       <c r="F56">
-        <v>-4.007168578305203</v>
+        <v>-4.832395762633939</v>
       </c>
       <c r="G56">
-        <v>-4.80681395732392</v>
+        <v>-5.95158074153066</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.457254800586993</v>
       </c>
       <c r="E57">
-        <v>-14.99402405370057</v>
+        <v>-15.88717045375939</v>
       </c>
       <c r="F57">
-        <v>-3.775686203174996</v>
+        <v>-4.681480466686926</v>
       </c>
       <c r="G57">
-        <v>-5.036863766847874</v>
+        <v>-5.803480176285825</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.440282445440746</v>
       </c>
       <c r="E58">
-        <v>-14.23684961419606</v>
+        <v>-15.14781103100105</v>
       </c>
       <c r="F58">
-        <v>-4.066898046906001</v>
+        <v>-4.67370051137733</v>
       </c>
       <c r="G58">
-        <v>-4.936855496652031</v>
+        <v>-6.517061646184651</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.432967609352552</v>
       </c>
       <c r="E59">
-        <v>-14.81794339886032</v>
+        <v>-15.15897371942996</v>
       </c>
       <c r="F59">
-        <v>-4.18628730104732</v>
+        <v>-4.672867482065809</v>
       </c>
       <c r="G59">
-        <v>-5.655565001591188</v>
+        <v>-6.296387301627911</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.434082430895742</v>
       </c>
       <c r="E60">
-        <v>-14.28920330219874</v>
+        <v>-13.84618721850236</v>
       </c>
       <c r="F60">
-        <v>-4.228931750232357</v>
+        <v>-5.193217024319213</v>
       </c>
       <c r="G60">
-        <v>-5.710145965897151</v>
+        <v>-6.094761836104139</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.443198738773305</v>
       </c>
       <c r="E61">
-        <v>-13.10187817365364</v>
+        <v>-15.12558528057141</v>
       </c>
       <c r="F61">
-        <v>-4.27524168675868</v>
+        <v>-5.25620813525286</v>
       </c>
       <c r="G61">
-        <v>-5.83474827890424</v>
+        <v>-6.966355644592379</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.45735566300795</v>
       </c>
       <c r="E62">
-        <v>-12.33017638953253</v>
+        <v>-13.44007366949448</v>
       </c>
       <c r="F62">
-        <v>-4.600629112291911</v>
+        <v>-4.827417383088756</v>
       </c>
       <c r="G62">
-        <v>-5.872700372966445</v>
+        <v>-6.054813483081753</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.475337634654178</v>
       </c>
       <c r="E63">
-        <v>-12.64722844023155</v>
+        <v>-13.21662970500801</v>
       </c>
       <c r="F63">
-        <v>-4.676601860614415</v>
+        <v>-5.209777837076963</v>
       </c>
       <c r="G63">
-        <v>-5.716823336249861</v>
+        <v>-6.192532177515435</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.49329366135176</v>
       </c>
       <c r="E64">
-        <v>-11.8942201968141</v>
+        <v>-13.24015512747786</v>
       </c>
       <c r="F64">
-        <v>-4.584722370077237</v>
+        <v>-5.034881274305408</v>
       </c>
       <c r="G64">
-        <v>-6.253178061249344</v>
+        <v>-6.500763830494818</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.509938642876651</v>
       </c>
       <c r="E65">
-        <v>-12.57385810435928</v>
+        <v>-12.53503096821751</v>
       </c>
       <c r="F65">
-        <v>-4.437934211745859</v>
+        <v>-4.96414663329822</v>
       </c>
       <c r="G65">
-        <v>-5.456041732484852</v>
+        <v>-6.786314935984654</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.520550553240225</v>
       </c>
       <c r="E66">
-        <v>-11.96144992193198</v>
+        <v>-11.9575056210713</v>
       </c>
       <c r="F66">
-        <v>-4.658318767673624</v>
+        <v>-5.20109754495444</v>
       </c>
       <c r="G66">
-        <v>-6.478795050296214</v>
+        <v>-7.030096888405506</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.523564993035428</v>
       </c>
       <c r="E67">
-        <v>-12.08974159056928</v>
+        <v>-12.02223562853694</v>
       </c>
       <c r="F67">
-        <v>-4.581452017361855</v>
+        <v>-5.409990730759776</v>
       </c>
       <c r="G67">
-        <v>-6.347339908022835</v>
+        <v>-7.30484899434624</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.514275531706907</v>
       </c>
       <c r="E68">
-        <v>-11.48971425607895</v>
+        <v>-12.90459973198349</v>
       </c>
       <c r="F68">
-        <v>-4.640567008067463</v>
+        <v>-5.368964829020317</v>
       </c>
       <c r="G68">
-        <v>-6.912443410485348</v>
+        <v>-6.374102358162302</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.493131981650483</v>
       </c>
       <c r="E69">
-        <v>-11.23786317414236</v>
+        <v>-13.35299564280099</v>
       </c>
       <c r="F69">
-        <v>-4.756808646701845</v>
+        <v>-5.792629125136143</v>
       </c>
       <c r="G69">
-        <v>-6.249539771701685</v>
+        <v>-7.043908484395345</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.458779103739265</v>
       </c>
       <c r="E70">
-        <v>-11.25368566232516</v>
+        <v>-11.6203380888302</v>
       </c>
       <c r="F70">
-        <v>-4.810048880314131</v>
+        <v>-5.357977077378998</v>
       </c>
       <c r="G70">
-        <v>-6.938977432982606</v>
+        <v>-6.408565137226115</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.416015721747501</v>
       </c>
       <c r="E71">
-        <v>-11.69705496699414</v>
+        <v>-11.46320004076404</v>
       </c>
       <c r="F71">
-        <v>-4.851327383147103</v>
+        <v>-5.8384758276822</v>
       </c>
       <c r="G71">
-        <v>-6.333240294571079</v>
+        <v>-6.367656725997342</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.366367316103332</v>
       </c>
       <c r="E72">
-        <v>-11.04271764372982</v>
+        <v>-12.77588238678947</v>
       </c>
       <c r="F72">
-        <v>-4.62048244964786</v>
+        <v>-5.981274630812586</v>
       </c>
       <c r="G72">
-        <v>-6.005466491273378</v>
+        <v>-6.745750821491964</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.315744306360637</v>
       </c>
       <c r="E73">
-        <v>-11.33267583444096</v>
+        <v>-11.99316282540769</v>
       </c>
       <c r="F73">
-        <v>-5.088222073243323</v>
+        <v>-6.102725078202848</v>
       </c>
       <c r="G73">
-        <v>-5.713267810340684</v>
+        <v>-5.999431366755286</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.264947886209075</v>
       </c>
       <c r="E74">
-        <v>-11.35267810413283</v>
+        <v>-11.86022947091253</v>
       </c>
       <c r="F74">
-        <v>-5.134172508526841</v>
+        <v>-5.59125299945844</v>
       </c>
       <c r="G74">
-        <v>-5.574046128232174</v>
+        <v>-6.093695840440494</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.218125559531803</v>
       </c>
       <c r="E75">
-        <v>-11.61984448516336</v>
+        <v>-12.27920388610219</v>
       </c>
       <c r="F75">
-        <v>-5.161353653153529</v>
+        <v>-6.400260659654204</v>
       </c>
       <c r="G75">
-        <v>-5.644338941667519</v>
+        <v>-6.00350002722305</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.171971220780905</v>
       </c>
       <c r="E76">
-        <v>-12.10786001507397</v>
+        <v>-12.87912706569034</v>
       </c>
       <c r="F76">
-        <v>-5.305436841781336</v>
+        <v>-6.233612037290257</v>
       </c>
       <c r="G76">
-        <v>-5.854926053966099</v>
+        <v>-6.395018384879418</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.124922389725424</v>
       </c>
       <c r="E77">
-        <v>-13.44584747385426</v>
+        <v>-13.56308060896483</v>
       </c>
       <c r="F77">
-        <v>-5.391926189235316</v>
+        <v>-6.068096556508808</v>
       </c>
       <c r="G77">
-        <v>-4.568808906869096</v>
+        <v>-6.979005239097934</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.068831475958081</v>
       </c>
       <c r="E78">
-        <v>-12.48189838268552</v>
+        <v>-14.44298575102522</v>
       </c>
       <c r="F78">
-        <v>-5.422981078531168</v>
+        <v>-6.578559814585081</v>
       </c>
       <c r="G78">
-        <v>-5.485939269250011</v>
+        <v>-5.817768490833319</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.999059501229048</v>
       </c>
       <c r="E79">
-        <v>-13.65471428051004</v>
+        <v>-13.80912618722358</v>
       </c>
       <c r="F79">
-        <v>-5.297755868091455</v>
+        <v>-6.309621210848816</v>
       </c>
       <c r="G79">
-        <v>-5.254399714233384</v>
+        <v>-5.774767814823726</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.905917634063456</v>
       </c>
       <c r="E80">
-        <v>-14.16074408002316</v>
+        <v>-14.80288169431081</v>
       </c>
       <c r="F80">
-        <v>-5.827347126214407</v>
+        <v>-6.425268959764908</v>
       </c>
       <c r="G80">
-        <v>-4.787381055008398</v>
+        <v>-5.843954906048954</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.785636160955332</v>
       </c>
       <c r="E81">
-        <v>-14.5856145683708</v>
+        <v>-14.83606182336501</v>
       </c>
       <c r="F81">
-        <v>-5.639240872402171</v>
+        <v>-6.800805224963487</v>
       </c>
       <c r="G81">
-        <v>-4.174940061879846</v>
+        <v>-6.124162791038406</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.632599219878808</v>
       </c>
       <c r="E82">
-        <v>-15.38157991622501</v>
+        <v>-16.71069156595027</v>
       </c>
       <c r="F82">
-        <v>-6.037262594188159</v>
+        <v>-6.311630933655509</v>
       </c>
       <c r="G82">
-        <v>-5.056518475714527</v>
+        <v>-5.018049936548196</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.450781465618511</v>
       </c>
       <c r="E83">
-        <v>-15.92404581760385</v>
+        <v>-16.86945986465919</v>
       </c>
       <c r="F83">
-        <v>-5.854051575360547</v>
+        <v>-6.495107619150436</v>
       </c>
       <c r="G83">
-        <v>-4.196696967163936</v>
+        <v>-5.09171288534252</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.243402238348974</v>
       </c>
       <c r="E84">
-        <v>-16.5296929883377</v>
+        <v>-17.82672492819261</v>
       </c>
       <c r="F84">
-        <v>-6.075501965369402</v>
+        <v>-6.794060617396109</v>
       </c>
       <c r="G84">
-        <v>-4.388738403351518</v>
+        <v>-5.735186932356199</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.023893091426887</v>
       </c>
       <c r="E85">
-        <v>-17.44570365366124</v>
+        <v>-19.08370251544969</v>
       </c>
       <c r="F85">
-        <v>-6.430077090924183</v>
+        <v>-6.995870678494643</v>
       </c>
       <c r="G85">
-        <v>-3.971728845042763</v>
+        <v>-4.631712582660787</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.802537781420164</v>
       </c>
       <c r="E86">
-        <v>-19.75475443627633</v>
+        <v>-19.44610723333554</v>
       </c>
       <c r="F86">
-        <v>-6.21579297018269</v>
+        <v>-6.927854468691307</v>
       </c>
       <c r="G86">
-        <v>-4.689835830693772</v>
+        <v>-5.573387329669859</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.598903619683146</v>
       </c>
       <c r="E87">
-        <v>-20.63603170596104</v>
+        <v>-21.12863910851542</v>
       </c>
       <c r="F87">
-        <v>-6.587695422158293</v>
+        <v>-7.244685527089898</v>
       </c>
       <c r="G87">
-        <v>-3.875762750950369</v>
+        <v>-4.512675296705214</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.425353944680474</v>
       </c>
       <c r="E88">
-        <v>-21.2269296368519</v>
+        <v>-23.14824794645624</v>
       </c>
       <c r="F88">
-        <v>-6.30023300218209</v>
+        <v>-6.948329806545545</v>
       </c>
       <c r="G88">
-        <v>-4.041472107918588</v>
+        <v>-5.685614823451153</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.302949127970751</v>
       </c>
       <c r="E89">
-        <v>-23.13775547218047</v>
+        <v>-23.9664979149022</v>
       </c>
       <c r="F89">
-        <v>-6.720892612249849</v>
+        <v>-6.947257637640792</v>
       </c>
       <c r="G89">
-        <v>-4.311586139558803</v>
+        <v>-5.107414802835282</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.241929367946875</v>
       </c>
       <c r="E90">
-        <v>-24.8673698916181</v>
+        <v>-25.29063730016704</v>
       </c>
       <c r="F90">
-        <v>-6.585340847388514</v>
+        <v>-7.302118622113309</v>
       </c>
       <c r="G90">
-        <v>-4.292100268514653</v>
+        <v>-5.673365804955849</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.262409539762652</v>
       </c>
       <c r="E91">
-        <v>-26.56705562633904</v>
+        <v>-27.60407164562155</v>
       </c>
       <c r="F91">
-        <v>-6.574374871703532</v>
+        <v>-7.276995503323736</v>
       </c>
       <c r="G91">
-        <v>-4.863490496956242</v>
+        <v>-4.412008227947055</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.369631474790738</v>
       </c>
       <c r="E92">
-        <v>-28.48583346202508</v>
+        <v>-29.03405958234167</v>
       </c>
       <c r="F92">
-        <v>-6.639076385025853</v>
+        <v>-7.499700980270577</v>
       </c>
       <c r="G92">
-        <v>-4.36406490744733</v>
+        <v>-5.531839983152006</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.579519171805342</v>
       </c>
       <c r="E93">
-        <v>-30.67021988368301</v>
+        <v>-30.02314849696399</v>
       </c>
       <c r="F93">
-        <v>-6.578135381399743</v>
+        <v>-6.89472809205806</v>
       </c>
       <c r="G93">
-        <v>-5.215229339412727</v>
+        <v>-5.052026065417736</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.889411430562592</v>
       </c>
       <c r="E94">
-        <v>-32.88641657100781</v>
+        <v>-31.61159906039752</v>
       </c>
       <c r="F94">
-        <v>-6.722752674847533</v>
+        <v>-7.123123428432597</v>
       </c>
       <c r="G94">
-        <v>-5.896582648486748</v>
+        <v>-6.576903067352516</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.304712705559263</v>
       </c>
       <c r="E95">
-        <v>-33.87888825571387</v>
+        <v>-36.33052936364547</v>
       </c>
       <c r="F95">
-        <v>-6.661044761631872</v>
+        <v>-7.006787559296246</v>
       </c>
       <c r="G95">
-        <v>-6.071667470422184</v>
+        <v>-5.685306942716</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.817632418844994</v>
       </c>
       <c r="E96">
-        <v>-36.69681498375589</v>
+        <v>-36.97889136545668</v>
       </c>
       <c r="F96">
-        <v>-6.579837469332362</v>
+        <v>-7.382153576108915</v>
       </c>
       <c r="G96">
-        <v>-5.667145289887558</v>
+        <v>-6.298671578050008</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.416885903005883</v>
       </c>
       <c r="E97">
-        <v>-39.06028670275816</v>
+        <v>-40.09969602055371</v>
       </c>
       <c r="F97">
-        <v>-6.267640730368826</v>
+        <v>-7.527121264490495</v>
       </c>
       <c r="G97">
-        <v>-6.081056177571556</v>
+        <v>-8.079000205431571</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.096202356543785</v>
       </c>
       <c r="E98">
-        <v>-41.54183611727342</v>
+        <v>-40.43004367093926</v>
       </c>
       <c r="F98">
-        <v>-6.776873844875282</v>
+        <v>-7.156196354991198</v>
       </c>
       <c r="G98">
-        <v>-7.541433820764716</v>
+        <v>-8.561263926864902</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.81982610766246</v>
       </c>
       <c r="E99">
-        <v>-43.34951916436628</v>
+        <v>-43.59561682007612</v>
       </c>
       <c r="F99">
-        <v>-6.473324536136524</v>
+        <v>-6.483949223196729</v>
       </c>
       <c r="G99">
-        <v>-7.389731381973153</v>
+        <v>-7.990410006800674</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.5970579055491</v>
       </c>
       <c r="E100">
-        <v>-46.09406876382502</v>
+        <v>-45.78453171574172</v>
       </c>
       <c r="F100">
-        <v>-6.144719020183119</v>
+        <v>-7.016107272682128</v>
       </c>
       <c r="G100">
-        <v>-8.164597670894967</v>
+        <v>-8.669296959447937</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.347198517476492</v>
       </c>
       <c r="E101">
-        <v>-48.52821071607249</v>
+        <v>-48.76375702734445</v>
       </c>
       <c r="F101">
-        <v>-5.623148044742432</v>
+        <v>-6.474877359786612</v>
       </c>
       <c r="G101">
-        <v>-7.909192393085734</v>
+        <v>-9.859785688097553</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.139908667815387</v>
       </c>
       <c r="E102">
-        <v>-50.43876031448659</v>
+        <v>-51.1820663023426</v>
       </c>
       <c r="F102">
-        <v>-5.736135167720587</v>
+        <v>-6.708359163635062</v>
       </c>
       <c r="G102">
-        <v>-8.702872512307227</v>
+        <v>-9.590088785195286</v>
       </c>
     </row>
   </sheetData>
